--- a/data/out/variants/v1_original/raw_v1_original.xlsx
+++ b/data/out/variants/v1_original/raw_v1_original.xlsx
@@ -550,7 +550,7 @@
         <v>9639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.04395484924316406</v>
+        <v>0.05042004585266113</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>9639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03755593299865723</v>
+        <v>0.02994775772094727</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>9639</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8730707168579102</v>
+        <v>0.756906270980835</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>9639</v>
       </c>
       <c r="N5" t="n">
-        <v>5.294975996017456</v>
+        <v>4.855203866958618</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>9639</v>
       </c>
       <c r="N6" t="n">
-        <v>1.387962102890015</v>
+        <v>1.256908655166626</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>9639</v>
       </c>
       <c r="N7" t="n">
-        <v>366.4686653614044</v>
+        <v>420.9705970287323</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>9639</v>
       </c>
       <c r="N8" t="n">
-        <v>291.3660855293274</v>
+        <v>576.1426184177399</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>9639</v>
       </c>
       <c r="N9" t="n">
-        <v>181.9452183246613</v>
+        <v>165.4067060947418</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>9639</v>
       </c>
       <c r="N10" t="n">
-        <v>1.931688785552979</v>
+        <v>2.290177822113037</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 849, 'learning_rate': 0.048365142854106334, 'max_depth': 3, 'subsample': 0.7528342198314617, 'colsample_bytree': 0.8962319339584381}</t>
+          <t>{'n_estimators': 506, 'learning_rate': 0.09830525658815337, 'max_depth': 3, 'subsample': 0.8933134814996085, 'colsample_bytree': 0.6362063042197921}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>-0.1821527006161288</v>
+        <v>0.03020953963708706</v>
       </c>
       <c r="G11" t="n">
-        <v>316.5085360654121</v>
+        <v>286.9146825250554</v>
       </c>
       <c r="H11" t="n">
-        <v>297065.2375468413</v>
+        <v>243700.3555701548</v>
       </c>
       <c r="I11" t="n">
-        <v>545.0369139304615</v>
+        <v>493.6601620246005</v>
       </c>
       <c r="J11" t="n">
-        <v>44.5513490089681</v>
+        <v>44.67652320109522</v>
       </c>
       <c r="K11" t="n">
         <v>48192</v>
@@ -1076,7 +1076,7 @@
         <v>9639</v>
       </c>
       <c r="N11" t="n">
-        <v>91.41843676567078</v>
+        <v>66.03011155128479</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 794, 'learning_rate': 0.016202485791222482, 'num_leaves': 31, 'min_child_samples': 34}</t>
+          <t>{'n_estimators': 572, 'learning_rate': 0.015071053100350531, 'num_leaves': 31, 'min_child_samples': 41}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>-0.02311408270773185</v>
+        <v>-0.0187742994212412</v>
       </c>
       <c r="G12" t="n">
-        <v>282.5205463598263</v>
+        <v>281.0263418568586</v>
       </c>
       <c r="H12" t="n">
-        <v>257100.1426961883</v>
+        <v>256009.5908984118</v>
       </c>
       <c r="I12" t="n">
-        <v>507.0504340755348</v>
+        <v>505.9739033768558</v>
       </c>
       <c r="J12" t="n">
-        <v>38.15427921524063</v>
+        <v>37.93919063696136</v>
       </c>
       <c r="K12" t="n">
         <v>48192</v>
@@ -1134,7 +1134,7 @@
         <v>9639</v>
       </c>
       <c r="N12" t="n">
-        <v>153.2875025272369</v>
+        <v>151.8182697296143</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 994, 'learning_rate': 0.09985968916779565, 'depth': 4}</t>
+          <t>{'iterations': 685, 'learning_rate': 0.0986297984444477, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>-0.130926807723369</v>
+        <v>-0.09678493017753897</v>
       </c>
       <c r="G13" t="n">
-        <v>313.4592470948206</v>
+        <v>307.4545001869331</v>
       </c>
       <c r="H13" t="n">
-        <v>284192.5925553732</v>
+        <v>275613.0199179626</v>
       </c>
       <c r="I13" t="n">
-        <v>533.0971698999847</v>
+        <v>524.988590274077</v>
       </c>
       <c r="J13" t="n">
-        <v>44.65494040880502</v>
+        <v>44.95067143869066</v>
       </c>
       <c r="K13" t="n">
         <v>48192</v>
@@ -1192,7 +1192,7 @@
         <v>9639</v>
       </c>
       <c r="N13" t="n">
-        <v>155.241587638855</v>
+        <v>119.8547737598419</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>427.4897957049567</v>
       </c>
       <c r="J14" t="n">
-        <v>54.80113211906639</v>
+        <v>54.80113211906641</v>
       </c>
       <c r="K14" t="n">
         <v>48192</v>
@@ -1250,7 +1250,7 @@
         <v>9639</v>
       </c>
       <c r="N14" t="n">
-        <v>239.8261811733246</v>
+        <v>78.78300309181213</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>9639</v>
       </c>
       <c r="N15" t="n">
-        <v>55.68148875236511</v>
+        <v>14.49403786659241</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>9639</v>
       </c>
       <c r="N16" t="n">
-        <v>3866.483611106873</v>
+        <v>2092.731700897217</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
